--- a/output7/【河洛文讀注音-雅俗通】《正氣歌》.xlsx
+++ b/output7/【河洛文讀注音-雅俗通】《正氣歌》.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A91755C-EFD8-44DC-8E38-765CFA76F15B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2FC919A4-DEB6-445E-8B67-D8F3A49A918F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{33AB2257-ECDF-4521-8F0E-4FD5B627422C}"/>
+    <workbookView minimized="1" xWindow="795" yWindow="2640" windowWidth="28695" windowHeight="11295" activeTab="4" xr2:uid="{33AB2257-ECDF-4521-8F0E-4FD5B627422C}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="10" r:id="rId1"/>
@@ -42,7 +42,6 @@
     <definedName name="顯示注音輸入">env!$C$10</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/output7/【河洛文讀注音-雅俗通】《正氣歌》.xlsx
+++ b/output7/【河洛文讀注音-雅俗通】《正氣歌》.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2FC919A4-DEB6-445E-8B67-D8F3A49A918F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C23BDE21-824D-4CDC-831B-BFA574B2B12C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="795" yWindow="2640" windowWidth="28695" windowHeight="11295" activeTab="4" xr2:uid="{33AB2257-ECDF-4521-8F0E-4FD5B627422C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{33AB2257-ECDF-4521-8F0E-4FD5B627422C}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="10" r:id="rId1"/>

--- a/output7/【河洛文讀注音-雅俗通】《正氣歌》.xlsx
+++ b/output7/【河洛文讀注音-雅俗通】《正氣歌》.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C23BDE21-824D-4CDC-831B-BFA574B2B12C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836CD361-99AF-4140-9BE6-6A93E32CE7C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{33AB2257-ECDF-4521-8F0E-4FD5B627422C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{33AB2257-ECDF-4521-8F0E-4FD5B627422C}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="10" r:id="rId1"/>
